--- a/vijayasaradhi95/clarification_prd.xlsx
+++ b/vijayasaradhi95/clarification_prd.xlsx
@@ -3155,7 +3155,9 @@
       <c r="P40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
+      <c r="A41" t="n">
+        <v>160</v>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>vijaya</t>
@@ -3166,23 +3168,39 @@
           <t>design</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>ME Platform, ME Product</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>The system should be fast and easy to use.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="M41" t="inlineStr">
         <is>
           <t>inscope</t>

--- a/vijayasaradhi95/clarification_prd.xlsx
+++ b/vijayasaradhi95/clarification_prd.xlsx
@@ -3178,7 +3178,11 @@
           <t>Performance</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Recycled Plastic Content</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
           <t>ME Platform, ME Product</t>
@@ -3189,7 +3193,11 @@
           <t>The system should be fast and easy to use.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Align with HP's corporate goal to increase recycled content plastic to 30% by product weight by 2025.</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
           <t>Accept - Threshold</t>

--- a/vijayasaradhi95/clarification_prd.xlsx
+++ b/vijayasaradhi95/clarification_prd.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,61 +512,61 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Chua, Cheryl</t>
+          <t>Rajesh Kumar</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Product Steward</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Legacy</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Environmental &amp; Sustainability compliance</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Recycled Plastic Content</t>
+          <t>Response Time</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ME Platform, ME Product</t>
+          <t>SKU-1001</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>The binary image stored in flash memory initializes the device at startup, directly interfaces with hardware registers, and operates independently of any operating system.</t>
+          <t>API response time should be under 2 seconds</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Align with HP's corporate goal to increase recycled content plastic to 30% by product weight by 2025.</t>
+          <t>Improve user experience and reduce latency</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Accept - Threshold</t>
+          <t>≤ 2.5 sec</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.4 to 0.6 (RCP content)</t>
+          <t>≤ 2 sec</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>High Want</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -580,57 +580,61 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>160</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>vijaya</t>
+          <t>Priya Sharma</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Legacy</t>
+          <t>Non-Functional</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Reliability</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Recycled Plastic Content</t>
+          <t>Uptime</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ME Platform, ME Product</t>
+          <t>SKU-1002</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>The system should be fast and easy to use.</t>
+          <t>System uptime must be 99.5% monthly</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Align with HP's corporate goal to increase recycled content plastic to 30% by product weight by 2025.</t>
+          <t>Ensure system availability</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>≥ 99%</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>≥ 99.9%</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -641,6 +645,2570 @@
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Amit Verma</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Monitoring</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Alerts</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>SKU-1003</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Automated alerts for critical system failures</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Reduce downtime and faster issue resolution</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Alert within 10 mins</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Alert within 5 mins</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Sneha Reddy</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SKU-1004</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Implement multi-factor authentication</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Enhance system security</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Optional MFA</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Mandatory MFA</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Arjun Patel</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Enhancement</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Usability</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>UI Improvement</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>SKU-1005</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Improve dashboard layout responsiveness</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Better user interaction</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Works on desktop</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Works on all devices</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kavya Nair</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Non-Functional</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Data Encryption</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>SKU-1006</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Encrypt sensitive data at rest and in transit</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Meet compliance requirements</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>AES-128</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>AES-256</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Rahul Singh</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Audit Logs</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SKU-1007</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Generate downloadable audit reports</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Improve transparency</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Monthly reports</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Weekly reports</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Neha Gupta</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Invoice Accuracy</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SKU-1008</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Ensure invoice calculation accuracy</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Avoid revenue leakage</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>98% accuracy</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>100% accuracy</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Vikram Joshi</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Non-Functional</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Scalability</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Load Handling</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SKU-1009</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Support 5,000 concurrent users</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Handle peak traffic</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>3,000 users</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>5,000 users</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Pooja Mehta</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Enhancement</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>CRM Sync</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SKU-1010</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Integrate system with CRM platform</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Improve customer data visibility</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Daily sync</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Real-time sync</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>58</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Itsushi Wakabayashi</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Connectivity Self-Heal</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Please update if needed</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Increase heal rate if it is not 90% or higher</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Chong, Shin</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>DVAR</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Print Quality</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Marconi Base LP1, Marconi Hi, PDL SKUs, Manhattan Base &amp; Hi, Malbec Hi, Agave</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Tilt printer left and right to 20 degrees while printing to assess for PQ (Print Quality) issues when printing on a trolley.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>tilt 20 degree is for CISS product as acknowledged by Michelle. Shin to check if want to evaluate on Manhattan Plus with XXL ink cartridges. Close for Marconi.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Meet customer requirement</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Chong, Shin</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>DVAR</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Mechanical Integrity</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Marconi Base LP2, Marconi Base LP1, Marconi Hi, PDL SKUs, Manhattan Base &amp; Hi, Malbec Hi, Agave</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Clear paper jam and check if encoder strip will drop when printer is tilted left and right to 20 degrees during printing.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20220704(Sau Pin): Marconi Base LP2 test no issue reported. 20220315(Sau Pin): Marconi Base LP1 test with no issue reported. Marconi Hi and PDL SKUs testing on-going interesting to find out the test result. HDRV response: Have conducted sanity check with Manhattan Base &amp; Hi, Malbec Hi and Agave. No issue found. Agree to put it as evaluation. To be consistent with standard UBT requirement.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Meet customer requirement</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Tracy Foo</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Mechanical Robustness</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>LP1</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Improve robustness of gate handoff to prevent breakage or deformation during paper jam events. Target for LP1.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20220315 (Sau Pin): Design Changed aligned and released for LP1 testing 20210607 (Jeffrey/TH): Under investigation, budget catered make proto to verify new design. Close up the slot, similar to sayan. Stronger piece. Target for LP1.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Better than current Manhattan units.</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>8</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Tracy Foo</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Sensor Feedback</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>CD1, CD2, Cleanout latch process</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Improve feedback for cleanout/duplexer missing by adding a dedicated sensor and improving firmware feedback. Sensor should not be tied to other sensors.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20220315(Sau Pin): Design improvement to Cleanout to prevent/limit twist implemented. Need final alignment with requestor 20210607 (Jeffrey/TH): Improved solution planned &amp; to be verified in CD2; CD1 design as threshold/back-up, budget catered Is it possible to add conduct circuit to detect latch? plan prototype to improve cleanout latch process to reduce the issue. 20210617AQ: it would be very expensive to add cleanout sensor (estimate $0.8~1)</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Better than current Manhattan units.</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Tracy Foo</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Print System Reliability</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Manhattan, Yeti, Marconi</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Eliminate Print System Problem by identifying root cause and implementing fix to prevent field failures.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20230307(SP): No reported incident. Will change status to "Green". 20221209(SP): To monitor until MC checkpoint 202210315(Sau Pin):This is on-going investigation in Manhattan. Will apply fix, if any and qualified 20210607 (Jeffrey): To follow up with Pock Chueng Current issue on Manhattan and Yeti. the current team need to continue investigate the unknown root cause. If identified then we look for opportunity to implement on Marconi. Pauline is working on it for Manhattan and Yeti. 20220118 (AQ, Boon Hock, Tracy, ZJ) the PSP taskforce is still working on this issue. We continue checking field return units. So far most of the returned units are recoverable therefore difficult to find out the root cause of the failure. May request more EE resource on this taskforce (to identify the EE support).</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Better than or equal to current Manhattan</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Tracy Foo</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Paper Handling</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Manhattan, Marconi</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Implement paper de-skew function so printer can correct skewed paper during pick and guide media to a straight path.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>202200316(SP): This is already in current Manhattan product.No change to Marconi program When Paper is skewed during pick, printer can move the media in and out and guide the media to a straight path into the paper path (Normal and Best)</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>as per current Manhattan, Turn roller deskew and Feed roller deskew</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>WANT</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Tracy Foo</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Media Handling</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Manhattan, Marconi Base LP2</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Improve pick of special media such as card or thick media by adding ribs on tray to increase stiffness and help media pick.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>20220704(SP): Marconi Base LP2 DET completed and meeting intervention. Change to "Green" as Threshold is same as Manhattan 20220315(SP): Need to clarify with Requestor on the issue. Change to "Yellow" as Threshold is same as Manhattan investigate card media pick improvements. Plan to add ribs on tray to increase the stiffness, which will help media pick.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>as per current manhattan</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Tracy Foo</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Cosmetic Quality</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Manhattan, SF, 3M</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>No cosmetic aerosol should be visible on new White case parts for 3M; requirement is stricter than Manhattan.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>20230307(SP):  SF 10K review  and Hi 15K review with TEM. Aligned to keep to current condition. Similar to Manhattan 20221129 (ZJ): AIO expectation is the same as Manhattan =&gt; Status to be Green. SF status check WIP =&gt; Status Yellow 20220315(SP): Test on-going. Will review after LP1 test are completed undergoing aerosol test for batch priming currently.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Same as Manhattan</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>WANT</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>14</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Itsushi Wakabayashi</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Duty Cycle</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Marconi Hi, Manhattan</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Printer must achieve minimum 30,000 pages duty cycle, goal 50,000 pages for Marconi Hi.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>20221129(SP/ZJ): XXL supplies confirmed. No impact to Duty Cycle. change status to Green 20220926(Sau Pin): With XL supplies removed, page yield will reduce and will impact duty cycle numbers 20220316(SP): No Change from Manhattan 20210702 (Mandy, Jeffrey): Review when LP1 result available (w/o HW change, test more than predecessor) Waste ink is the bottleneck. We cannot do more than 30k in a month, ink will flow out. 20211011 (Jeffrey): Based on aligned mech lift with Waka Marconi Hi PDL will be about 30K, therefore accept Threshold</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Min 30,000 pages, goal 50,000</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>15</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Itsushi Wakabayashi</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Duty Cycle</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Marconi Base</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>The printer must withstand tilting left and right at 20 degrees while printing for a minimum of 25,000 pages, with a goal of 30,000 pages, without functional failure.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>tilt 20 degree is for CISS product as acknoledged by Michelle. Shin to check if want to evaluate on Manhattan Plus with XXL ink cartridges. Close for Marconi. Threshold should be manhattan base 20k, waste ink for manhattan base is 20k in a month. Based on aligned mech life with Waka, will target 25K Duty cycle, so accept Threshold.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Min 25,000 pages</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Goal 30,000 pages</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>16</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Itsushi Wakabayashi</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Monthly Recommended Print volume</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Marconi Base, Marconi Hi</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>The printer should support a monthly recommended print volume of 1,500 pages for Marconi Base and 2,000 pages for Marconi Hi while tilted left and right at 20 degrees during printing.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>tilt 20 degree is for CISS product as acknoledged by Michelle. Shin to check if want to evaluate on Manhattan Plus with XXL ink cartridges. Close for Marconi. Need Clarification.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>1,500 for Marconi Base, 2,000 for Marconi Hi</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>1,500 for Marconi Base, 2,000 for Marconi Hi</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>17</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Itsushi Wakabayashi</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Mech Life</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Marconi Hi</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>The printer must achieve a mechanical life of at least 60,000 pages (target 100,000 pages) for Marconi Hi SKU while tilted left and right at 20 degrees during printing.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>No Hardware reliability issue to meet 60K for Hi/PDL-hi. Base LP2 Life test completed. PDL-Base on-going. Hi/PDl-Hi LP2 test ongoing. LP1 test still on-going. DDO test in progress, but only 2 units. aerosol test in progress. full qual will be in LP1.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>60,000 pages</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>100,000 pages</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>18</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Itsushi Wakabayashi</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Mech Life</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Marconi Base</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>The printer must achieve a mechanical life of at least 45,000 pages (target 80,000 pages) for Marconi Base SKU while tilted left and right at 20 degrees during printing.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Marconi Base LP2 DET completed and no hardware failure reported. LP1 test completed with defect investigation on-going. aerosol test in progress.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>45,000 pages</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>80,000 pages</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>19</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Itsushi Wakabayashi</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Borderless Printing</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>The printer must support borderless photo printing and enable 100% copy reproduction while tilted left and right at 20 degrees during printing.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Same as Manhattan. Manhattan/Malbec support 4x6 borderless photo copy. As the printout need to be borderless, the reproduction photo is actually magnified a little bit. We want to know if the request is to follow Malbec, or is there anything new.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Support borderless photo printing</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Enable 100% copy reproduction</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>21</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Itsushi Wakabayashi</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Input tray capacity</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Input Tray Capacity</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Marconi Base, Marconi Hi</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>The printer must maintain Manhattan input tray capacity: Marconi Base 250 sheets, Marconi Hi 250 + 250 sheets, while tilted left and right at 20 degrees during printing.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>No Change from Manhattan program, same as Manhattan.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Marconi Base 250 sheets, Marconi Hi 250 + 250 sheets</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Maintain Manhattan input tray capacity</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>22</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Itsushi Wakabayashi</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Output paper tray</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Output Paper Tray Capacity</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Marconi Base, Marconi Hi</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>The printer should support an output paper tray capacity of 100 sheets for both Marconi Base and Marconi Hi SKUs while tilted left and right at 20 degrees during printing.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Output Management Test with LP2 Life Test units show same performance as Manhattan. Need to review Marconi Base LP1 testing result. Need to conduct RnD validation test for Base SKU to support up to 80 sheets. Manhattan Base can accommodate around 80 sheets without ME modification. To align with marketing to test up to 80 on Marconi Base.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>100 sheets for both Marconi Base and Marconi Hi</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>100 sheets output paper tray capacity</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>23</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Itsushi Wakabayashi</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Media Size</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Media Size Supported</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>The printer must support the following media sizes: Letter, Legal, Government Legal, Executive, Statement, 3x5 in, 4x6 in, 5x7 in, 13x18 cm, 8x10 in, 10x15 cm, L, Photo 2L, Envelope (#10, Monarch, 5.5 bar), Card (3x5 in, 4x6 in, 5x8 in), Hagaki, 5x5, 4x5, and 4x12 inch HP branded photo media while tilted left and right at 20 degrees during printing.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Mech is able to support these media size. New media size added need to evaluated performance and accept as it is. Accept.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Support listed media sizes</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Support listed media sizes</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>24</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Mandy Hagedorn</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Media Sizes</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Expanded Photo Media Handling</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Marconi Base</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>The printer must support expanded photo media handling for 5x5 and 4x12 inch sizes for Marconi Base SKU while tilted left and right at 20 degrees during printing.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Marconi Base LP2 DET completed and able to support expanded photo media handling for 5x5 and 4x12. LP1 test with media still on-going. Follow Novelli solution.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Support expanded photo media handling for 5x5 and 4x12 inch sizes</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Support expanded photo media handling for 5x5 and 4x12 inch sizes</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>25</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Mandy Hagedorn</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Simplex and Duplex Printing</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Assess functional failure when printer is tilted left and right at 20 degrees during printing. Follow Novelli solution for simplex and duplex print on brochure and photo media. Wider bottom margin (0.50 inch) and less ink on first side, with UI changes for media type selection.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Follow Novelli solution and align with TME and Marketing to drop this. Novelli investigated duplex on 4x6 Photo Matte media and proposed UI changes for media type selection to avoid mech limitation issues.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Follow Novelli solution</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>26</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Ben / Ricker</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>OPS</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Print Quality</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Remove LDV, change to 4HC. Print quality should be same as Malbec. Evaluate functional failure when printer is tilted left and right at 20 degrees during printing. Accept threshold for drop.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>No change from Manhattan. Marconi has bigger swath height and printmode is more sensitive to linefeed error. LDV cannot be removed but parameter setting may be possible per vendor.</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Same as Manhattan</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Celine Taccori</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Quiet Mode</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>GxD</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Quiet mode activation during printing must be instantaneous and result in a noticeable reduction in noise, confirmed by user perception.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Same as Manhattan/Malbec. Majority delivered in FW BR3 except trigger in middle of printing planned post BR3.1. User must hear difference when quiet mode is activated.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Quiet mode should be instantaneous and hearable</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Tracy Foo</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Printer Noise</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Printer noise during operation must meet threshold as per Blue Angel item 153 activities, unless throughput increase is required.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>No change from Manhattan. Follow-up on Acoustic Testing with Marconi units. Blue Angel is a goal, not a threshold, as it conflicts with throughput.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Same as Manhattan</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Tracy Foo</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>PHA Rejection</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>PHA Rejection issue (62.80.A0): Find a fix to eliminate this issue. Workaround is to remove and re-install PHA. Monitor and implement animation prompt for re-seat as in Manhattan.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Issue reported during Manhattan launch. Root cause unknown. Animation prompt rolled out in Manhattan to reduce returns. Monitor and implement similar solution for Marconi.</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Better than or equal to current Manhattan</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>High Want</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Tracy Foo</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Customer Experience</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Carriage Movement Lock</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Improve carriage movement lock during transportation in moving vehicles. Solution should be better than Manhattan and prevent carriage-related returns.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Carriage related returns are top 3 for Mobile products. Current lock insufficient. Goal is better than Manhattan. No issues captured on user handling or vibration tests.</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Better than current Manhattan</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Chua, Cheryl</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Product Steward</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Sustainability compliance</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Plastic Marking</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>ME Platform, ME Product</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Smaller plastic parts (&lt;25g) must have material code whenever feasible, per HP GSE product requirement section 4.2.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Align with HP GSE product requirement section 4.2 for plastic marking.</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Plastic Parts &gt;25g has material code marking</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>33</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Chua, Cheryl</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Product Steward</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Sustainability compliance</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>IZOD Impact Test</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>ME Platform, ME Product</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Perform IZOD Impact test if applicable when spray paint is used for EPEAT compliance.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Required for EPEAT compliance when spray paint is applied.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Required for EPEAT</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>34</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Chua, Cheryl</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Product Steward</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Sustainability compliance</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Recycled Plastic Content</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>ME Platform, ME Product</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Increase recycled content plastic to 30% by product weight by 2025, with RCP measured across product family.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Align with HP's corporate goal to increase recycled content plastic to 30% by product weight by 2025.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0.4 to 0.6 (RCP content)</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>High Want</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Chua, Cheryl</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Product Steward</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Sustainability compliance</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Recycled Plastic Content</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>ME Platform, ME Product</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>The binary image stored in flash memory initializes the device at startup, directly interfaces with hardware registers, and operates independently of any operating system.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Align with HP's corporate goal to increase recycled content plastic to 30% by product weight by 2025.</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0.4 to 0.6 (RCP content)</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>High Want</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>160</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>vijaya</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>design</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>ME Platform, ME Product</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>The system should be fast and easy to use.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/vijayasaradhi95/clarification_prd.xlsx
+++ b/vijayasaradhi95/clarification_prd.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,82 +417,82 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Item No.</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Requestor</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Requestor Function</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>SubCategory</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>SKUs Applicable</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Requirement (What)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Justification (Why)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>New Threshold (Acceptable to Ship)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Target (Design Goal)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Ambiguity Score</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Clarification Questions</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Response</t>
         </is>

--- a/vijayasaradhi95/clarification_prd.xlsx
+++ b/vijayasaradhi95/clarification_prd.xlsx
@@ -562,7 +562,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
     </row>
@@ -630,7 +634,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
     </row>
@@ -698,7 +706,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
@@ -766,7 +778,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
@@ -834,7 +850,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
@@ -902,7 +922,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
     </row>
@@ -970,7 +994,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
     </row>
@@ -1038,7 +1066,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
@@ -1106,7 +1138,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
@@ -1174,7 +1210,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
@@ -1242,7 +1282,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
     </row>
@@ -1310,7 +1354,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
     </row>
@@ -1378,7 +1426,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
     </row>
@@ -1446,7 +1498,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
     </row>
@@ -1514,7 +1570,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
     </row>
@@ -1582,7 +1642,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
     </row>
@@ -1650,7 +1714,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
     </row>
@@ -1718,7 +1786,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
     </row>
@@ -1786,7 +1858,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
     </row>
@@ -1854,7 +1930,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
     </row>
@@ -1922,7 +2002,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
     </row>
@@ -1990,7 +2074,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
     </row>
@@ -2058,7 +2146,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
     </row>
@@ -2126,7 +2218,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
     </row>
@@ -2190,7 +2286,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
     </row>
@@ -2258,7 +2358,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
     </row>
@@ -2326,7 +2430,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
     </row>
@@ -2390,7 +2498,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
     </row>
@@ -2458,7 +2570,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
     </row>
@@ -2526,7 +2642,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
     </row>
@@ -2594,7 +2714,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
     </row>
@@ -2662,7 +2786,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
     </row>
@@ -2730,7 +2858,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
     </row>
@@ -2798,7 +2930,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
     </row>
@@ -2866,7 +3002,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
     </row>
@@ -2934,7 +3074,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
     </row>
@@ -3002,7 +3146,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
     </row>
@@ -3070,7 +3218,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
     </row>
@@ -3138,7 +3290,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
     </row>
@@ -3194,7 +3350,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
     </row>

--- a/vijayasaradhi95/clarification_prd.xlsx
+++ b/vijayasaradhi95/clarification_prd.xlsx
@@ -562,7 +562,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
     </row>
@@ -630,7 +634,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
     </row>
@@ -698,7 +706,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
@@ -766,7 +778,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
@@ -834,7 +850,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
@@ -902,7 +922,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
     </row>
@@ -970,7 +994,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
     </row>
@@ -1038,7 +1066,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
@@ -1106,7 +1138,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
@@ -1174,7 +1210,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>

--- a/vijayasaradhi95/clarification_prd.xlsx
+++ b/vijayasaradhi95/clarification_prd.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,82 +429,82 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Item No.</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Requestor</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Requestor Function</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>SubCategory</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>SKUs Applicable</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Requirement (What)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Justification (Why)</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>New Threshold (Acceptable to Ship)</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Target (Design Goal)</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Ambiguity Score</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Clarification Questions</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Response</t>
         </is>
@@ -562,11 +574,7 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
     </row>
@@ -634,11 +642,7 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
     </row>
@@ -706,11 +710,7 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
@@ -778,11 +778,7 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
@@ -850,11 +846,7 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
@@ -922,11 +914,7 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
     </row>
@@ -994,11 +982,7 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
     </row>
@@ -1066,11 +1050,7 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
@@ -1138,11 +1118,7 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
@@ -1210,11 +1186,7 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>

--- a/vijayasaradhi95/clarification_prd.xlsx
+++ b/vijayasaradhi95/clarification_prd.xlsx
@@ -574,7 +574,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
     </row>
@@ -642,7 +646,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
     </row>
@@ -710,8 +718,16 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>What qualifies as a 'critical system failure'? Is the alert mechanism defined (email, SMS, etc.)? Who receives the alerts?</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -778,7 +794,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
@@ -846,8 +866,16 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>What devices are included in 'all devices'? Are there specific responsiveness metrics or UI guidelines to follow?</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -914,7 +942,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
     </row>
@@ -982,8 +1014,16 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>What format should the audit reports be in? What information must be included in the reports? Who can access/download these reports?</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -1050,7 +1090,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
@@ -1118,7 +1162,11 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
@@ -1186,8 +1234,16 @@
           <t>inscope</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Which CRM platform(s) must be supported? What does 'real-time sync' mean in terms of latency or update frequency?</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr"/>
     </row>
   </sheetData>

--- a/vijayasaradhi95/clarification_prd.xlsx
+++ b/vijayasaradhi95/clarification_prd.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="inscope" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -719,4 +720,2814 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Item No.</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Requestor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Requestor Function</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>SubCategory</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>SKUs Applicable</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Requirement (What)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Justification (Why)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>New Threshold (Acceptable to Ship)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Target (Design Goal)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Ambiguity Score</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Clarification Questions</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Response</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Rajesh Kumar</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Response Time</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>SKU-1001</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>API response time should be under 2 seconds</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Improve user experience and reduce latency</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>≤ 2.5 sec</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>≤ 2 sec</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>What is the maximum acceptable response time in milliseconds?
+Which component — frontend, backend, or network — owns this response time requirement?
+Under what load conditions (concurrent users, requests/second) must this be met?</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Priya Sharma</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Non-Functional</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Uptime</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>SKU-1002</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>System uptime must be 99.5% monthly</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Ensure system availability</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>≥ 99%</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>≥ 99.9%</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Amit Verma</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Monitoring</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Alerts</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>SKU-1003</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Automated alerts for critical system failures</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Reduce downtime and faster issue resolution</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Alert within 10 mins</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Alert within 5 mins</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Sneha Reddy</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SKU-1004</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Implement multi-factor authentication</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Enhance system security</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Optional MFA</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Mandatory MFA</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Arjun Patel</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Enhancement</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Usability</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>UI Improvement</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>SKU-1005</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Improve dashboard layout responsiveness</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Better user interaction</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Works on desktop</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Works on all devices</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kavya Nair</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Non-Functional</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Data Encryption</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>SKU-1006</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Encrypt sensitive data at rest and in transit</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Meet compliance requirements</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>AES-128</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>AES-256</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Rahul Singh</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Audit Logs</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SKU-1007</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Generate downloadable audit reports</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Improve transparency</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Monthly reports</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Weekly reports</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Neha Gupta</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Invoice Accuracy</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SKU-1008</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Ensure invoice calculation accuracy</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Avoid revenue leakage</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>98% accuracy</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>100% accuracy</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Vikram Joshi</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Non-Functional</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Scalability</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Load Handling</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SKU-1009</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Support 5,000 concurrent users</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Handle peak traffic</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>3,000 users</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>5,000 users</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Pooja Mehta</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Enhancement</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>CRM Sync</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SKU-1010</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Integrate system with CRM platform</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Improve customer data visibility</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Daily sync</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Real-time sync</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>58</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Itsushi Wakabayashi</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Connectivity Self-Heal</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Please update if needed</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Increase heal rate if it is not 90% or higher</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Chong, Shin</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>DVAR</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Print Quality</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Marconi Base LP1, Marconi Hi, PDL SKUs, Manhattan Base &amp; Hi, Malbec Hi, Agave</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Tilt printer left and right to 20 degrees while printing to assess for PQ (Print Quality) issues when printing on a trolley.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>tilt 20 degree is for CISS product as acknowledged by Michelle. Shin to check if want to evaluate on Manhattan Plus with XXL ink cartridges. Close for Marconi.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Meet customer requirement</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Chong, Shin</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>DVAR</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Mechanical Integrity</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Marconi Base LP2, Marconi Base LP1, Marconi Hi, PDL SKUs, Manhattan Base &amp; Hi, Malbec Hi, Agave</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Clear paper jam and check if encoder strip will drop when printer is tilted left and right to 20 degrees during printing.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20220704(Sau Pin): Marconi Base LP2 test no issue reported. 20220315(Sau Pin): Marconi Base LP1 test with no issue reported. Marconi Hi and PDL SKUs testing on-going interesting to find out the test result. HDRV response: Have conducted sanity check with Manhattan Base &amp; Hi, Malbec Hi and Agave. No issue found. Agree to put it as evaluation. To be consistent with standard UBT requirement.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Meet customer requirement</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Tracy Foo</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Mechanical Robustness</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>LP1</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Improve robustness of gate handoff to prevent breakage or deformation during paper jam events. Target for LP1.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20220315 (Sau Pin): Design Changed aligned and released for LP1 testing 20210607 (Jeffrey/TH): Under investigation, budget catered make proto to verify new design. Close up the slot, similar to sayan. Stronger piece. Target for LP1.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Better than current Manhattan units.</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>8</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Tracy Foo</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Sensor Feedback</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>CD1, CD2, Cleanout latch process</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Improve feedback for cleanout/duplexer missing by adding a dedicated sensor and improving firmware feedback. Sensor should not be tied to other sensors.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20220315(Sau Pin): Design improvement to Cleanout to prevent/limit twist implemented. Need final alignment with requestor 20210607 (Jeffrey/TH): Improved solution planned &amp; to be verified in CD2; CD1 design as threshold/back-up, budget catered Is it possible to add conduct circuit to detect latch? plan prototype to improve cleanout latch process to reduce the issue. 20210617AQ: it would be very expensive to add cleanout sensor (estimate $0.8~1)</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Better than current Manhattan units.</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Tracy Foo</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Print System Reliability</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Manhattan, Yeti, Marconi</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Eliminate Print System Problem by identifying root cause and implementing fix to prevent field failures.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20230307(SP): No reported incident. Will change status to "Green". 20221209(SP): To monitor until MC checkpoint 202210315(Sau Pin):This is on-going investigation in Manhattan. Will apply fix, if any and qualified 20210607 (Jeffrey): To follow up with Pock Chueng Current issue on Manhattan and Yeti. the current team need to continue investigate the unknown root cause. If identified then we look for opportunity to implement on Marconi. Pauline is working on it for Manhattan and Yeti. 20220118 (AQ, Boon Hock, Tracy, ZJ) the PSP taskforce is still working on this issue. We continue checking field return units. So far most of the returned units are recoverable therefore difficult to find out the root cause of the failure. May request more EE resource on this taskforce (to identify the EE support).</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Better than or equal to current Manhattan</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Tracy Foo</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Paper Handling</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Manhattan, Marconi</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Implement paper de-skew function so printer can correct skewed paper during pick and guide media to a straight path.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>202200316(SP): This is already in current Manhattan product.No change to Marconi program When Paper is skewed during pick, printer can move the media in and out and guide the media to a straight path into the paper path (Normal and Best)</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>as per current Manhattan, Turn roller deskew and Feed roller deskew</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>WANT</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Tracy Foo</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Media Handling</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Manhattan, Marconi Base LP2</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Improve pick of special media such as card or thick media by adding ribs on tray to increase stiffness and help media pick.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>20220704(SP): Marconi Base LP2 DET completed and meeting intervention. Change to "Green" as Threshold is same as Manhattan 20220315(SP): Need to clarify with Requestor on the issue. Change to "Yellow" as Threshold is same as Manhattan investigate card media pick improvements. Plan to add ribs on tray to increase the stiffness, which will help media pick.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>as per current manhattan</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Tracy Foo</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Cosmetic Quality</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Manhattan, SF, 3M</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>No cosmetic aerosol should be visible on new White case parts for 3M; requirement is stricter than Manhattan.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>20230307(SP):  SF 10K review  and Hi 15K review with TEM. Aligned to keep to current condition. Similar to Manhattan 20221129 (ZJ): AIO expectation is the same as Manhattan =&gt; Status to be Green. SF status check WIP =&gt; Status Yellow 20220315(SP): Test on-going. Will review after LP1 test are completed undergoing aerosol test for batch priming currently.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Same as Manhattan</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>WANT</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>14</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Itsushi Wakabayashi</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Duty Cycle</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Marconi Hi, Manhattan</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Printer must achieve minimum 30,000 pages duty cycle, goal 50,000 pages for Marconi Hi.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>20221129(SP/ZJ): XXL supplies confirmed. No impact to Duty Cycle. change status to Green 20220926(Sau Pin): With XL supplies removed, page yield will reduce and will impact duty cycle numbers 20220316(SP): No Change from Manhattan 20210702 (Mandy, Jeffrey): Review when LP1 result available (w/o HW change, test more than predecessor) Waste ink is the bottleneck. We cannot do more than 30k in a month, ink will flow out. 20211011 (Jeffrey): Based on aligned mech lift with Waka Marconi Hi PDL will be about 30K, therefore accept Threshold</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Min 30,000 pages, goal 50,000</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>15</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Itsushi Wakabayashi</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Duty Cycle</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Marconi Base</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>The printer must withstand tilting left and right at 20 degrees while printing for a minimum of 25,000 pages, with a goal of 30,000 pages, without functional failure.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>tilt 20 degree is for CISS product as acknoledged by Michelle. Shin to check if want to evaluate on Manhattan Plus with XXL ink cartridges. Close for Marconi. Threshold should be manhattan base 20k, waste ink for manhattan base is 20k in a month. Based on aligned mech life with Waka, will target 25K Duty cycle, so accept Threshold.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Min 25,000 pages</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Goal 30,000 pages</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>16</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Itsushi Wakabayashi</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Monthly Recommended Print volume</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Marconi Base, Marconi Hi</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>The printer should support a monthly recommended print volume of 1,500 pages for Marconi Base and 2,000 pages for Marconi Hi while tilted left and right at 20 degrees during printing.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>tilt 20 degree is for CISS product as acknoledged by Michelle. Shin to check if want to evaluate on Manhattan Plus with XXL ink cartridges. Close for Marconi. Need Clarification.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>1,500 for Marconi Base, 2,000 for Marconi Hi</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>1,500 for Marconi Base, 2,000 for Marconi Hi</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>17</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Itsushi Wakabayashi</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Mech Life</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Marconi Hi</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>The printer must achieve a mechanical life of at least 60,000 pages (target 100,000 pages) for Marconi Hi SKU while tilted left and right at 20 degrees during printing.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>No Hardware reliability issue to meet 60K for Hi/PDL-hi. Base LP2 Life test completed. PDL-Base on-going. Hi/PDl-Hi LP2 test ongoing. LP1 test still on-going. DDO test in progress, but only 2 units. aerosol test in progress. full qual will be in LP1.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>60,000 pages</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>100,000 pages</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>18</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Itsushi Wakabayashi</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Mech Life</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Marconi Base</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>The printer must achieve a mechanical life of at least 45,000 pages (target 80,000 pages) for Marconi Base SKU while tilted left and right at 20 degrees during printing.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Marconi Base LP2 DET completed and no hardware failure reported. LP1 test completed with defect investigation on-going. aerosol test in progress.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>45,000 pages</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>80,000 pages</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>19</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Itsushi Wakabayashi</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Borderless Printing</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>The printer must support borderless photo printing and enable 100% copy reproduction while tilted left and right at 20 degrees during printing.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Same as Manhattan. Manhattan/Malbec support 4x6 borderless photo copy. As the printout need to be borderless, the reproduction photo is actually magnified a little bit. We want to know if the request is to follow Malbec, or is there anything new.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Support borderless photo printing</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Enable 100% copy reproduction</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>21</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Itsushi Wakabayashi</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Input tray capacity</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Input Tray Capacity</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Marconi Base, Marconi Hi</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>The printer must maintain Manhattan input tray capacity: Marconi Base 250 sheets, Marconi Hi 250 + 250 sheets, while tilted left and right at 20 degrees during printing.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>No Change from Manhattan program, same as Manhattan.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Marconi Base 250 sheets, Marconi Hi 250 + 250 sheets</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Maintain Manhattan input tray capacity</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>22</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Itsushi Wakabayashi</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Output paper tray</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Output Paper Tray Capacity</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Marconi Base, Marconi Hi</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>The printer should support an output paper tray capacity of 100 sheets for both Marconi Base and Marconi Hi SKUs while tilted left and right at 20 degrees during printing.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Output Management Test with LP2 Life Test units show same performance as Manhattan. Need to review Marconi Base LP1 testing result. Need to conduct RnD validation test for Base SKU to support up to 80 sheets. Manhattan Base can accommodate around 80 sheets without ME modification. To align with marketing to test up to 80 on Marconi Base.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>100 sheets for both Marconi Base and Marconi Hi</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>100 sheets output paper tray capacity</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>23</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Itsushi Wakabayashi</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Media Size</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Media Size Supported</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>The printer must support the following media sizes: Letter, Legal, Government Legal, Executive, Statement, 3x5 in, 4x6 in, 5x7 in, 13x18 cm, 8x10 in, 10x15 cm, L, Photo 2L, Envelope (#10, Monarch, 5.5 bar), Card (3x5 in, 4x6 in, 5x8 in), Hagaki, 5x5, 4x5, and 4x12 inch HP branded photo media while tilted left and right at 20 degrees during printing.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Mech is able to support these media size. New media size added need to evaluated performance and accept as it is. Accept.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Support listed media sizes</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Support listed media sizes</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>24</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Mandy Hagedorn</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Media Sizes</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Expanded Photo Media Handling</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Marconi Base</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>The printer must support expanded photo media handling for 5x5 and 4x12 inch sizes for Marconi Base SKU while tilted left and right at 20 degrees during printing.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Marconi Base LP2 DET completed and able to support expanded photo media handling for 5x5 and 4x12. LP1 test with media still on-going. Follow Novelli solution.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Support expanded photo media handling for 5x5 and 4x12 inch sizes</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Support expanded photo media handling for 5x5 and 4x12 inch sizes</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>25</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Mandy Hagedorn</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Simplex and Duplex Printing</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Assess functional failure when printer is tilted left and right at 20 degrees during printing. Follow Novelli solution for simplex and duplex print on brochure and photo media. Wider bottom margin (0.50 inch) and less ink on first side, with UI changes for media type selection.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Follow Novelli solution and align with TME and Marketing to drop this. Novelli investigated duplex on 4x6 Photo Matte media and proposed UI changes for media type selection to avoid mech limitation issues.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Follow Novelli solution</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>26</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Ben / Ricker</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>OPS</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Print Quality</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Remove LDV, change to 4HC. Print quality should be same as Malbec. Evaluate functional failure when printer is tilted left and right at 20 degrees during printing. Accept threshold for drop.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>No change from Manhattan. Marconi has bigger swath height and printmode is more sensitive to linefeed error. LDV cannot be removed but parameter setting may be possible per vendor.</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Same as Manhattan</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Celine Taccori</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Quiet Mode</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>GxD</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Quiet mode activation during printing must be instantaneous and result in a noticeable reduction in noise, confirmed by user perception.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Same as Manhattan/Malbec. Majority delivered in FW BR3 except trigger in middle of printing planned post BR3.1. User must hear difference when quiet mode is activated.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Quiet mode should be instantaneous and hearable</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Tracy Foo</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Printer Noise</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Printer noise during operation must meet threshold as per Blue Angel item 153 activities, unless throughput increase is required.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>No change from Manhattan. Follow-up on Acoustic Testing with Marconi units. Blue Angel is a goal, not a threshold, as it conflicts with throughput.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Same as Manhattan</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Tracy Foo</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>PHA Rejection</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>PHA Rejection issue (62.80.A0): Find a fix to eliminate this issue. Workaround is to remove and re-install PHA. Monitor and implement animation prompt for re-seat as in Manhattan.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Issue reported during Manhattan launch. Root cause unknown. Animation prompt rolled out in Manhattan to reduce returns. Monitor and implement similar solution for Marconi.</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Better than or equal to current Manhattan</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>High Want</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Tracy Foo</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Customer Experience</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Carriage Movement Lock</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Improve carriage movement lock during transportation in moving vehicles. Solution should be better than Manhattan and prevent carriage-related returns.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Carriage related returns are top 3 for Mobile products. Current lock insufficient. Goal is better than Manhattan. No issues captured on user handling or vibration tests.</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Better than current Manhattan</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Chua, Cheryl</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Product Steward</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Sustainability compliance</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Plastic Marking</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>ME Platform, ME Product</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Smaller plastic parts (&lt;25g) must have material code whenever feasible, per HP GSE product requirement section 4.2.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Align with HP GSE product requirement section 4.2 for plastic marking.</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Plastic Parts &gt;25g has material code marking</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>33</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Chua, Cheryl</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Product Steward</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Sustainability compliance</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>IZOD Impact Test</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>ME Platform, ME Product</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Perform IZOD Impact test if applicable when spray paint is used for EPEAT compliance.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Required for EPEAT compliance when spray paint is applied.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Required for EPEAT</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>34</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Chua, Cheryl</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Product Steward</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Sustainability compliance</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Recycled Plastic Content</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>ME Platform, ME Product</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Increase recycled content plastic to 30% by product weight by 2025, with RCP measured across product family.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Align with HP's corporate goal to increase recycled content plastic to 30% by product weight by 2025.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0.4 to 0.6 (RCP content)</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>High Want</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Chua, Cheryl</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Product Steward</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Sustainability compliance</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Recycled Plastic Content</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>ME Platform, ME Product</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>The binary image stored in flash memory initializes the device at startup, directly interfaces with hardware registers, and operates independently of any operating system.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Align with HP's corporate goal to increase recycled content plastic to 30% by product weight by 2025.</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0.4 to 0.6 (RCP content)</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>High Want</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>160</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>vijaya</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>design</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>ME Platform, ME Product</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>The system should be fast and easy to use.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>